--- a/stories/arbres/ATOM-REL.CON.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honorine colle des papiers à l'atelier. Un camarade a un collage. Honorine passe trop vite. La colle tombe sur le collage. Le papier est collant. Le camarade a les yeux mouillés. Maman s'approche. Maman dit : tu peux dire pardon. Honorine dit : pardon. Maman dit : tu peux proposer un geste. Honorine tend une feuille neuve. C'est un geste simple. Le camarade prend la feuille. Il reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.</t>
+          <t>Honorine colle des papiers à l'atelier. Un camarade a un collage. Honorine passe trop vite. La colle tombe sur le collage. Le papier est collant. Le camarade a les yeux mouillés. Maman s'approche. Tu peux dire pardon. Pardon. Tu peux proposer un geste. Honorine tend une feuille neuve. C'est un geste simple. Le camarade prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine colle des papiers à l'atelier. Un camarade a un collage. Honorine passe trop vite. La colle tombe sur le collage. Le papier est collant. Le camarade a les yeux mouillés. Maman s'approche.
+maman|Tu peux dire pardon.
+enfant-f|Pardon.
+maman|Tu peux proposer un geste.
+narrateur|Honorine tend une feuille neuve. C'est un geste simple. Le camarade prend la feuille. Il reste un peu triste.
+maman|La peine reste un peu.
+narrateur|Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1465,6 +1492,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Le collage est collant. Que fait Honorine ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Honorine a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Le chiffon est posé. Maman reste assise près d'eux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1499,6 +1505,7 @@
           <t>narrateur|Le collage est collant. Que fait Honorine ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Honorine a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Le chiffon est posé. Maman reste assise près d'eux.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-REL.CON.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Honorine dit pardon et propose un geste</t>
+          <t>La colle sucrée et le seau</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Chouchou fait tomber de la colle sur le collage de Sarah. Il dit pardon et tend une feuille. Au jardin, le seau mouille un dessin. Encore pardon, encore un geste. La peine reste un peu.</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1184,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Honorine colle des papiers à l'atelier. Un camarade a un collage. Honorine passe trop vite. La colle tombe sur le collage. Le papier est collant. Le camarade a les yeux mouillés. Maman s'approche. Tu peux dire pardon. Pardon. Tu peux proposer un geste. Honorine tend une feuille neuve. C'est un geste simple. Le camarade prend la feuille. Il reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.</t>
+          <t>La colle sent le sucre, tout près. Des papiers roses et verts attendent. Ils sont fins, presque transparents. La fenêtre est ouverte sur le jardin. Une abeille tapote le bois, puis part. Maman coupe un carré jaune. Les ciseaux font un petit bruit sec. Un pot de paillettes est fermé, tout rond. Il capte un bout de soleil. Le tapis de l'atelier est rêche sous les genoux. Tu as senti la colle, Chouchou ? Oui, maman. Elle sent le sucre. Sarah fait un collage. Son soleil est presque collé. En ce moment, Chouchou passe près de la table. La colle tombe sur le collage. Le papier est collant. Le soleil jaune se froisse. Sarah a les yeux mouillés. Elle est triste. Sarah a de la peine, Chouchou. Tu peux dire pardon. Pardon, Sarah. Tu peux proposer un geste. Chouchou tend une feuille neuve. La feuille est lisse, un peu épaisse. Tu peux coller dessus. C'est un geste simple. Sarah prend la feuille. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Sarah s'assoit près de maman. Chouchou attend, les mains calmes. Sarah cache un peu le soleil froissé. Tu as le temps, Sarah. La colle fait un fil brillant, puis plus. On laisse du temps à Sarah. Tu attends avec moi ? Oui, maman. L'abeille ne tapote plus. Le carré jaune attend sur la table. Plus tard, au jardin, l'herbe est tiède. Sarah a dessiné à la craie, au sol. Un soleil blanc, tout rond. Chouchou bouscule un seau. L'eau mouille le dessin. La craie devient une flaque pâle. Pardon, Sarah. Je tends un chiffon. C'est un geste. Sarah prend le chiffon. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Chouchou. C'est du bon travail. Sarah a encore un peu de peine. C'est normal. Ils essuient doucement. Le chiffon sent l'eau et l'herbe. Les papiers roses restent à la fenêtre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1312,16 +1324,76 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Honorine colle des papiers à l'atelier. Un camarade a un collage. Honorine passe trop vite. La colle tombe sur le collage. Le papier est collant. Le camarade a les yeux mouillés. Maman s'approche.
+          <t>narrateur|La colle sent le sucre, tout près.
+narrateur|Des papiers roses et verts attendent.
+narrateur|Ils sont fins, presque transparents.
+narrateur|La fenêtre est ouverte sur le jardin.
+narrateur|Une abeille tapote le bois, puis part.
+narrateur|Maman coupe un carré jaune.
+narrateur|Les ciseaux font un petit bruit sec.
+narrateur|Un pot de paillettes est fermé, tout rond.
+narrateur|Il capte un bout de soleil.
+narrateur|Le tapis de l'atelier est rêche sous les genoux.
+maman|Tu as senti la colle, Chouchou ?
+enfant-m|Oui, maman.
+enfant-m|Elle sent le sucre.
+maman|Sarah fait un collage.
+maman|Son soleil est presque collé.
+narrateur|En ce moment, Chouchou passe près de la table.
+narrateur|La colle tombe sur le collage.
+narrateur|Le papier est collant.
+narrateur|Le soleil jaune se froisse.
+narrateur|Sarah a les yeux mouillés.
+narrateur|Elle est triste.
+maman|Sarah a de la peine, Chouchou.
 maman|Tu peux dire pardon.
-enfant-f|Pardon.
+enfant-m|Pardon, Sarah.
 maman|Tu peux proposer un geste.
-narrateur|Honorine tend une feuille neuve. C'est un geste simple. Le camarade prend la feuille. Il reste un peu triste.
+narrateur|Chouchou tend une feuille neuve.
+narrateur|La feuille est lisse, un peu épaisse.
+enfant-m|Tu peux coller dessus.
+narrateur|C'est un geste simple.
+narrateur|Sarah prend la feuille.
+narrateur|Elle reste un peu triste.
 maman|La peine reste un peu.
-narrateur|Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+maman|Le pardon n'efface pas tout de suite.
+narrateur|Sarah s'assoit près de maman.
+narrateur|Chouchou attend, les mains calmes.
+narrateur|Sarah cache un peu le soleil froissé.
+maman|Tu as le temps, Sarah.
+narrateur|La colle fait un fil brillant, puis plus.
+maman|On laisse du temps à Sarah.
+maman|Tu attends avec moi ?
+enfant-m|Oui, maman.
+narrateur|L'abeille ne tapote plus.
+narrateur|Le carré jaune attend sur la table.
+narrateur|Plus tard, au jardin, l'herbe est tiède.
+narrateur|Sarah a dessiné à la craie, au sol.
+narrateur|Un soleil blanc, tout rond.
+narrateur|Chouchou bouscule un seau.
+narrateur|L'eau mouille le dessin.
+narrateur|La craie devient une flaque pâle.
+enfant-m|Pardon, Sarah.
+enfant-m|Je tends un chiffon.
+narrateur|C'est un geste.
+narrateur|Sarah prend le chiffon.
+narrateur|La peine reste un peu.
+maman|Tu as dit pardon, encore.
+maman|Tu as proposé un geste.
+maman|Bravo, Chouchou.
+maman|C'est du bon travail.
+maman|Sarah a encore un peu de peine.
+maman|C'est normal.
+narrateur|Ils essuient doucement.
+narrateur|Le chiffon sent l'eau et l'herbe.
+narrateur|Les papiers roses restent à la fenêtre.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>abeille_fenetre,seau_eau</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,7 +1418,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Le collage est collant. Que fait Honorine ?</t>
+          <t>Le collage est collant. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1502,7 +1574,8 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Le collage est collant. Que fait Honorine ?</t>
+          <t>narrateur|Le collage est collant.
+narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1530,7 +1603,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Honorine a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>Chouchou a dit pardon. Il a proposé un geste. Il a tendu une feuille neuve. Bravo, Chouchou. C'est du bon travail. La peine de Sarah reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1674,7 +1747,15 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Honorine a dit pardon. Elle a proposé un geste. La peine reste un peu. Maman est là.</t>
+          <t>narrateur|Chouchou a dit pardon.
+narrateur|Il a proposé un geste.
+narrateur|Il a tendu une feuille neuve.
+maman|Bravo, Chouchou.
+maman|C'est du bon travail.
+maman|La peine de Sarah reste un peu.
+enfant-m|J'ai dit pardon.
+maman|Oui.
+maman|Et tu as attendu.</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr"/>
@@ -1702,7 +1783,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Le chiffon est posé. Maman reste assise près d'eux.</t>
+          <t>Le chiffon est posé près du seau. Sarah souffle un peu. On reste assis dans l'herbe ? Oui, maman. L'herbe est tiède, hein ? Elle pique un peu. La peine reste un peu. On laisse le temps. Je laisse du temps. Oui. C'est bien. Le carré jaune attend encore à la table. Le pot de paillettes n'a pas bougé. On collera le jaune plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1842,7 +1923,21 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Le chiffon est posé. Maman reste assise près d'eux.</t>
+          <t>narrateur|Le chiffon est posé près du seau.
+narrateur|Sarah souffle un peu.
+maman|On reste assis dans l'herbe ?
+enfant-m|Oui, maman.
+maman|L'herbe est tiède, hein ?
+enfant-m|Elle pique un peu.
+maman|La peine reste un peu.
+maman|On laisse le temps.
+enfant-m|Je laisse du temps.
+maman|Oui.
+maman|C'est bien.
+narrateur|Le carré jaune attend encore à la table.
+narrateur|Le pot de paillettes n'a pas bougé.
+maman|On collera le jaune plus tard.
+enfant-m|D'accord, maman.</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1870,7 +1965,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. Tu as fait du bon travail. La colle ne sent presque plus. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2010,7 +2105,12 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>enfant-m|J'ai dit pardon.
+enfant-m|J'ai tendu une feuille.
+maman|Bravo.
+maman|Tu as fait du bon travail.
+narrateur|La colle ne sent presque plus.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2032,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-06.xlsx
@@ -1184,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>La colle sent le sucre, tout près. Des papiers roses et verts attendent. Ils sont fins, presque transparents. La fenêtre est ouverte sur le jardin. Une abeille tapote le bois, puis part. Maman coupe un carré jaune. Les ciseaux font un petit bruit sec. Un pot de paillettes est fermé, tout rond. Il capte un bout de soleil. Le tapis de l'atelier est rêche sous les genoux. Tu as senti la colle, Chouchou ? Oui, maman. Elle sent le sucre. Sarah fait un collage. Son soleil est presque collé. En ce moment, Chouchou passe près de la table. La colle tombe sur le collage. Le papier est collant. Le soleil jaune se froisse. Sarah a les yeux mouillés. Elle est triste. Sarah a de la peine, Chouchou. Tu peux dire pardon. Pardon, Sarah. Tu peux proposer un geste. Chouchou tend une feuille neuve. La feuille est lisse, un peu épaisse. Tu peux coller dessus. C'est un geste simple. Sarah prend la feuille. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Sarah s'assoit près de maman. Chouchou attend, les mains calmes. Sarah cache un peu le soleil froissé. Tu as le temps, Sarah. La colle fait un fil brillant, puis plus. On laisse du temps à Sarah. Tu attends avec moi ? Oui, maman. L'abeille ne tapote plus. Le carré jaune attend sur la table. Plus tard, au jardin, l'herbe est tiède. Sarah a dessiné à la craie, au sol. Un soleil blanc, tout rond. Chouchou bouscule un seau. L'eau mouille le dessin. La craie devient une flaque pâle. Pardon, Sarah. Je tends un chiffon. C'est un geste. Sarah prend le chiffon. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Chouchou. C'est du bon travail. Sarah a encore un peu de peine. C'est normal. Ils essuient doucement. Le chiffon sent l'eau et l'herbe. Les papiers roses restent à la fenêtre.</t>
+          <t>La colle sent le sucre, tout près. Des papiers roses et verts attendent. Ils sont fins, presque transparents. La fenêtre est ouverte sur le jardin. Une abeille tapote le bois, puis part. Maman coupe un carré jaune. Les ciseaux font un petit bruit sec. Un pot de paillettes est fermé, tout rond. Il capte un bout de soleil. Le tapis de l'atelier est rêche sous les genoux. Tu as senti la colle, Chouchou ? Oui, maman. Elle sent le sucre. Sarah fait un collage. Son soleil est presque collé. En ce moment, Chouchou passe près de la table. La colle tombe sur le collage. Le papier est collant. Le soleil jaune se froisse. Sarah a les yeux mouillés. Elle est triste. Sarah a de la peine, Chouchou. Tu peux dire pardon. Pardon, Sarah. Tu peux proposer un geste. Chouchou tend une feuille neuve. La feuille est lisse, un peu épaisse. Tu peux coller dessus. C'est un geste simple. Sarah prend la feuille. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Sarah s'assoit près de maman. Chouchou attend, les mains calmes. Sarah cache un peu le soleil froissé. Tu as le temps, Sarah. La colle fait un fil brillant, puis plus. On laisse du temps à Sarah. Tu attends avec moi ? Oui, maman. L'abeille ne tapote plus. Le carré jaune attend sur la table. Plus tard, au jardin, l'herbe est tiède. Sarah a dessiné à la craie, au sol. Un soleil blanc, tout rond. Chouchou bouscule un seau. L'eau mouille le dessin. La craie devient une flaque pâle. Pardon, Sarah. Je tends un chiffon. C'est un geste. Sarah prend le chiffon. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Chouchou. Sarah a encore un peu de peine. C'est normal. Ils essuient doucement. Le chiffon sent l'eau et l'herbe. Les papiers roses restent à la fenêtre.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honorine colle des papiers à l'atelier. Un camarade a un collage. Honorine passe trop vite. La colle tombe sur le collage. Le papier est collant. Le camarade a les yeux mouillés. Maman s'approche. Maman dit : tu peux dire &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Honorine dit : pardon. Maman dit : tu peux proposer un geste. Honorine tend une feuille neuve. C'est un geste simple. Le camarade prend la feuille. Il reste un peu triste. Maman dit : la peine reste un peu. Le pardon n'efface pas tout de suite. Plus tard, au jardin, Honorine bouscule un seau. L'eau mouille un dessin au sol. Honorine dit encore : pardon. Elle tend un chiffon. C'est un geste. La peine reste un peu. Maman laisse du temps. Ils essuient doucement.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La colle sent le sucre, tout près. Des papiers roses et verts attendent. Ils sont fins, presque transparents. La fenêtre est ouverte sur le jardin. Une abeille tapote le bois, puis part. Maman coupe un carré jaune. Les ciseaux font un petit bruit sec. Un pot de paillettes est fermé, tout rond. Il capte un bout de soleil. Le tapis de l'atelier est rêche sous les genoux. Tu as senti la colle, Chouchou ? Oui, maman. Elle sent le sucre. Sarah fait un collage. Son soleil est presque collé. En ce moment, Chouchou passe près de la table. La colle tombe sur le collage. Le papier est collant. Le soleil jaune se froisse. Sarah a les yeux mouillés. Elle est triste. Sarah a de la peine, Chouchou. Tu peux dire pardon. Pardon, Sarah. Tu peux proposer un geste. Chouchou tend une feuille neuve. La feuille est lisse, un peu épaisse. Tu peux coller dessus. C'est un geste simple. Sarah prend la feuille. Elle reste un peu triste. La peine reste un peu. Le pardon n'efface pas tout de suite. Sarah s'assoit près de maman. Chouchou attend, les mains calmes. Sarah cache un peu le soleil froissé. Tu as le temps, Sarah. La colle fait un fil brillant, puis plus. On laisse du temps à Sarah. Tu attends avec moi ? Oui, maman. L'abeille ne tapote plus. Le carré jaune attend sur la table. Plus tard, au jardin, l'herbe est tiède. Sarah a dessiné à la craie, au sol. Un soleil blanc, tout rond. Chouchou bouscule un seau. L'eau mouille le dessin. La craie devient une flaque pâle. Pardon, Sarah. Je tends un chiffon. C'est un geste. Sarah prend le chiffon. La peine reste un peu. Tu as dit pardon, encore. Tu as proposé un geste. Bravo, Chouchou. Sarah a encore un peu de peine. C'est normal. Ils essuient doucement. Le chiffon sent l'eau et l'herbe. Les papiers roses restent à la fenêtre.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1381,7 +1381,6 @@
 maman|Tu as dit pardon, encore.
 maman|Tu as proposé un geste.
 maman|Bravo, Chouchou.
-maman|C'est du bon travail.
 maman|Sarah a encore un peu de peine.
 maman|C'est normal.
 narrateur|Ils essuient doucement.
@@ -1423,7 +1422,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le collage est collant. Que fait Honorine ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le collage est collant. Que fait Chouchou ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1578,7 +1577,6 @@
 narrateur|Que fait Chouchou ?</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1603,12 +1601,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Chouchou a dit pardon. Il a proposé un geste. Il a tendu une feuille neuve. Bravo, Chouchou. C'est du bon travail. La peine de Sarah reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
+          <t>Chouchou a dit pardon. Il a proposé un geste. Il a tendu une feuille neuve. Bravo, Chouchou. La peine de Sarah reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Honorine a dit &lt;emphasis level="moderate"&gt;pardon&lt;/emphasis&gt;. Elle a proposé un geste. La peine reste un peu. Maman est là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Chouchou a dit pardon. Il a proposé un geste. Il a tendu une feuille neuve. Bravo, Chouchou. La peine de Sarah reste un peu. J'ai dit pardon. Oui. Et tu as attendu.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1751,14 +1749,12 @@
 narrateur|Il a proposé un geste.
 narrateur|Il a tendu une feuille neuve.
 maman|Bravo, Chouchou.
-maman|C'est du bon travail.
 maman|La peine de Sarah reste un peu.
 enfant-m|J'ai dit pardon.
 maman|Oui.
 maman|Et tu as attendu.</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1788,7 +1784,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Le chiffon est posé. Maman reste &lt;emphasis level="moderate"&gt;assis&lt;/emphasis&gt;e près d'eux.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le chiffon est posé près du seau. Sarah souffle un peu. On reste assis dans l'herbe ? Oui, maman. L'herbe est tiède, hein ? Elle pique un peu. La peine reste un peu. On laisse le temps. Je laisse du temps. Oui. C'est bien. Le carré jaune attend encore à la table. Le pot de paillettes n'a pas bougé. On collera le jaune plus tard. D'accord, maman.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1940,7 +1936,6 @@
 enfant-m|D'accord, maman.</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1965,12 +1960,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. Tu as fait du bon travail. La colle ne sent presque plus. L'histoire est finie.</t>
+          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. La colle ne sent presque plus.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>J'ai dit pardon. J'ai tendu une feuille. Bravo. La colle ne sent presque plus.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -2108,12 +2103,9 @@
           <t>enfant-m|J'ai dit pardon.
 enfant-m|J'ai tendu une feuille.
 maman|Bravo.
-maman|Tu as fait du bon travail.
-narrateur|La colle ne sent presque plus.
-narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+narrateur|La colle ne sent presque plus.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2132,7 +2124,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2177,6 +2169,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-REL.CON.003-06.xlsx
+++ b/stories/arbres/ATOM-REL.CON.003-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>atelier puis jardin</t>
+          <t>atelier à la maison puis jardin</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Honorine, maman</t>
+          <t>Chouchou, Sarah, maman</t>
         </is>
       </c>
     </row>
